--- a/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:13:57+00:00</t>
+    <t>2025-05-20T08:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T08:55:00+00:00</t>
+    <t>2025-05-21T07:47:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:22+00:00</t>
+    <t>2025-05-21T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:53+00:00</t>
+    <t>2025-05-21T07:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:49:53+00:00</t>
+    <t>2025-05-21T07:50:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:50:26+00:00</t>
+    <t>2025-05-21T07:51:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:51:14+00:00</t>
+    <t>2025-05-21T07:52:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:52:53+00:00</t>
+    <t>2025-05-21T08:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="129">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Mapping du modèle métier Patient/CDA/FHIR</t>
+    <t>Mapping Métier/CDA/FHIR : "Patient/Usager"</t>
   </si>
   <si>
     <t>Title</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T08:04:56+00:00</t>
+    <t>2025-05-21T13:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,9 +82,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ce ConceptMap présente deux groupes de mapping : 
- - Groupe Mapping 1 : entre le modèle métier du Patient/Usager et l'élément CDA recordTarget
- - Groupe Mapping 2 : entre l'élément CDA recordTarget et le profil FHIR FrPatientDocument</t>
+    <t xml:space="preserve">Ce ConceptMap présente deux groupes de mapping : 
+ - Mapping 1 : entre le modèle métier \"patient\" et l'élément CDA \"recordTarget\"
+ - Mapping 2 : entre l'élément CDA \"recordTarget\" et le profil FHIR \"FrPatientDocument\" </t>
   </si>
   <si>
     <t>Purpose</t>
@@ -141,259 +141,265 @@
     <t>recordTarget.patientRole.telecom</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.nomsPrenoms</t>
+    <t>Patient.personnePhysique.nomsPrenomsPatient</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.name</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.nomsPrenoms.noms</t>
+    <t>Patient.personnePhysique.nomsPrenomsPatient.nom</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.name.family</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.nomsPrenoms.noms.nomNaissance</t>
+    <t>Patient.personnePhysique.nomsPrenomsPatient.nom.nomNaissance</t>
   </si>
   <si>
     <t>PrecordTarget.patientRole.patient.name.family@qualifier='BR'</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.nomsPrenoms.noms.nomUtilise</t>
+    <t>Patient.personnePhysique.nomsPrenomsPatient.nom.nomUtilise</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.name.family@qualifier='CL'</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.nomsPrenoms.prenoms</t>
+    <t>Patient.personnePhysique.nomsPrenomsPatient.prenom</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.name.given</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.nomsPrenoms.prenoms.listePrenoms</t>
-  </si>
-  <si>
-    <t>Patient.personnePhysique.nomsPrenoms.prenoms.premierPrenom</t>
+    <t>Patient.personnePhysique.nomsPrenomsPatient.prenom.listePrenoms</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.nomsPrenomsPatient.prenom.premierPrenom</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.name.given@qualifier='BR'</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.nomsPrenoms.prenoms.prenomUtilise</t>
+    <t>Patient.personnePhysique.nomsPrenomsPatient.prenom.prenomUtilise</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.name.given@qualifier='CL'</t>
   </si>
   <si>
-    <t>Patient.sexe</t>
+    <t>Patient.personnePhysique.sexe</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.administrativeGenderCode</t>
   </si>
   <si>
-    <t>Patient.dateNaissance</t>
+    <t>Patient.personnePhysique.dateNaissance</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.birthTime</t>
   </si>
   <si>
-    <t>Patient.indicateurDeces</t>
+    <t>Patient.personnePhysique.indicateurDeces</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.sdtc:deceasedInd</t>
   </si>
   <si>
-    <t>Patient.dateDeces</t>
+    <t>Patient.personnePhysique.dateDeces</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.sdtc:deceasedTime</t>
   </si>
   <si>
-    <t>Patient.grossesseMultiple</t>
+    <t>Patient.personnePhysique.grossesseMultiple</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.sdtc:multipleBirthInd</t>
   </si>
   <si>
-    <t>Patient.numeroOrdreNaissance</t>
+    <t>Patient.personnePhysique.numeroOrdreNaissance</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.sdtc:multipleBirthOrderNumber</t>
   </si>
   <si>
-    <t>Patient.representantPatient</t>
+    <t>Patient.personnePhysique.representantPatient</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.guardian</t>
   </si>
   <si>
-    <t>Patient.representantPatient.adresse</t>
+    <t>Patient.personnePhysique.representantPatient.adresse</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.guardian.addr</t>
   </si>
   <si>
-    <t>Patient.representantPatient.coordonneesTelecom</t>
+    <t>Patient.personnePhysique.representantPatient.coordonneesTelecom</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.guardian.telecom</t>
   </si>
   <si>
-    <t>Patient.representantPatient.personneRepresentantPatient.nomsPrenoms</t>
+    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenomsRepresentantPatient</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.guardian.guardianPerson.name</t>
   </si>
   <si>
-    <t>Patient.representantPatient.personneRepresentantPatient.nom</t>
+    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenomsRepresentantPatient.nom</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.guardian.guardianPerson.family</t>
   </si>
   <si>
-    <t>Patient.representantPatient.personneRepresentantPatient.prenom</t>
+    <t>Patient.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenomsRepresentantPatient.prenom</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.guardian.guardianPerson.given</t>
   </si>
   <si>
-    <t>Patient.representantPatient.structureRepresentantPatient</t>
+    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.guardian.guardianOrganization</t>
   </si>
   <si>
-    <t>Patient.representantPatient.structureRepresentantPatient.identifiant</t>
+    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.identifiant</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.guardian.guardianOrganization.id</t>
   </si>
   <si>
-    <t>Patient.representantPatient.structureRepresentantPatient.nom</t>
+    <t>Patient.personnePhysique.representantPatient.structureRepresentantPatient.nom</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.guardian.guardianOrganization.name</t>
   </si>
   <si>
-    <t>Patient.lieuNaissance</t>
+    <t>Patient.personnePhysique.lieuNaissance</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.birthPlace</t>
   </si>
   <si>
-    <t>Patient.lieuNaissance.adresseEtCodeOfficielGeographique</t>
+    <t>Patient.personnePhysique.lieuNaissance.nomLieuNaissance</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.birthPlace.place.name</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.birthPlace.place.addr</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.codeOfficielGeographiqueLieuNaissance</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.birthPlace.place.addr.county</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-fhir-document</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole</t>
+  </si>
+  <si>
+    <t>Patient.identifier</t>
+  </si>
+  <si>
+    <t>Patient.address</t>
+  </si>
+  <si>
+    <t>Patient.telecom</t>
+  </si>
+  <si>
+    <t>Patient.name</t>
+  </si>
+  <si>
+    <t>Patient.name.family</t>
+  </si>
+  <si>
+    <t>recordTarget.patientRole.patient.name.family@qualifier='BR'</t>
+  </si>
+  <si>
+    <t>Patient.name:officialname.family</t>
+  </si>
+  <si>
+    <t>Patient.name:usualname.family</t>
+  </si>
+  <si>
+    <t>Patient.name.given</t>
+  </si>
+  <si>
+    <t>Patient.name:officialname.birth-list-given-name</t>
+  </si>
+  <si>
+    <t>Patient.name:officialname.given</t>
+  </si>
+  <si>
+    <t>Patient.name:usualname.given</t>
+  </si>
+  <si>
+    <t>Patient.gender</t>
+  </si>
+  <si>
+    <t>Patient.birthDate</t>
+  </si>
+  <si>
+    <t>Patient.deceasedBoolean</t>
+  </si>
+  <si>
+    <t>Patient.deceasedDateTime</t>
+  </si>
+  <si>
+    <t>Patient.multipleBirthBoolean</t>
+  </si>
+  <si>
+    <t>Patient.multipleBirthInteger</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship:Role='GUARD'</t>
+  </si>
+  <si>
+    <t>Patient.contact.address</t>
+  </si>
+  <si>
+    <t>Patient.contact.telecom</t>
+  </si>
+  <si>
+    <t>Patient.contact.name</t>
+  </si>
+  <si>
+    <t>Patient.contact.name.family</t>
+  </si>
+  <si>
+    <t>Patient.contact.name.given</t>
+  </si>
+  <si>
+    <t>Patient.contact.organization</t>
+  </si>
+  <si>
+    <t>Patient.contact.organization.identifier</t>
+  </si>
+  <si>
+    <t>Patient.contact.organization.name</t>
+  </si>
+  <si>
+    <t>Patient.extension:birthPlace</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.birthPlace.place</t>
   </si>
   <si>
-    <t>Patient.lieuNaissance.nomLieuNaissance</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.birthPlace.place.name</t>
-  </si>
-  <si>
-    <t>Patient.lieuNaissance.CodeOfficielGeographique</t>
+    <t>Patient.extension:birthPlace.value[FRCoreAddressProfile]</t>
+  </si>
+  <si>
+    <t>Patient.extension:birthPlace.value[FRCoreAddressProfile].text</t>
   </si>
   <si>
     <t>recordTarget.patientRole.patient.birthPlace.place.country</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-fhir-document</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole</t>
-  </si>
-  <si>
-    <t>Patient.identifier</t>
-  </si>
-  <si>
-    <t>Patient.address</t>
-  </si>
-  <si>
-    <t>Patient.telecom</t>
-  </si>
-  <si>
-    <t>Patient.name</t>
-  </si>
-  <si>
-    <t>Patient.name.family</t>
-  </si>
-  <si>
-    <t>recordTarget.patientRole.patient.name.family@qualifier='BR'</t>
-  </si>
-  <si>
-    <t>Patient.name:officialname.family</t>
-  </si>
-  <si>
-    <t>Patient.name:usualname.family</t>
-  </si>
-  <si>
-    <t>Patient.name.given</t>
-  </si>
-  <si>
-    <t>Patient.name:officialname.birth-list-given-name</t>
-  </si>
-  <si>
-    <t>Patient.name:officialname.given</t>
-  </si>
-  <si>
-    <t>Patient.name:usualname.given</t>
-  </si>
-  <si>
-    <t>Patient.gender</t>
-  </si>
-  <si>
-    <t>Patient.birthDate</t>
-  </si>
-  <si>
-    <t>Patient.deceasedBoolean</t>
-  </si>
-  <si>
-    <t>Patient.deceasedDateTime</t>
-  </si>
-  <si>
-    <t>Patient.multipleBirthBoolean</t>
-  </si>
-  <si>
-    <t>Patient.multipleBirthInteger</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:Role='GUARD'</t>
-  </si>
-  <si>
-    <t>Patient.contact.address</t>
-  </si>
-  <si>
-    <t>Patient.contact.telecom</t>
-  </si>
-  <si>
-    <t>Patient.contact.name</t>
-  </si>
-  <si>
-    <t>Patient.contact.name.family</t>
-  </si>
-  <si>
-    <t>Patient.contact.name.given</t>
-  </si>
-  <si>
-    <t>Patient.contact.organization</t>
-  </si>
-  <si>
-    <t>Patient.contact.organization.identifier</t>
-  </si>
-  <si>
-    <t>Patient.contact.organization.name</t>
-  </si>
-  <si>
-    <t>Patient.extension:birthPlace</t>
-  </si>
-  <si>
-    <t>Patient.extension:birthPlace.value[FRCoreAddressProfile]</t>
-  </si>
-  <si>
-    <t>Patient.extension:birthPlace.value[FRCoreAddressProfile].text</t>
   </si>
   <si>
     <t>Patient.extension:birthPlace.value[FRCoreAddressProfile].extension:inseeCode</t>
@@ -1502,40 +1508,40 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E33" s="2"/>
     </row>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T13:48:36+00:00</t>
+    <t>2025-05-23T10:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPatientCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T10:50:09+00:00</t>
+    <t>2025-05-23T12:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
